--- a/unfold/samples/castdie/oil_pan_t1_드로우금형_부품표.xlsx
+++ b/unfold/samples/castdie/oil_pan_t1_드로우금형_부품표.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>79.95999999999999</v>
+        <v>107.42</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>59.51</v>
+        <v>59.91</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>671.67</v>
+        <v>655.3</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1062,14 +1062,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>• 주물 무게 어림 1,215 kg (리브 · 빈 곳 판 솔리드 × 7.2) — 베이스 326 · 펀치 80 · 누르개 60 · 상형 672</t>
+          <t>• 주물 무게 어림 1,226 kg (리브 · 빈 곳 판 솔리드 × 7.2) — 베이스 326 · 펀치 107 · 누르개 60 · 상형 655</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>• 형면은 격자 9 mm 의 B-스플라인 근사 (다이 R · 벽은 뭉뚱그려짐) — NC 데이터는 CAD 형면으로, 상형 형면 오프셋은 수직 t (법선 오프셋 아님)</t>
+          <t>• 형면은 격자 9 mm 의 B-스플라인 근사 (다이 R · 벽은 뭉뚱그려짐) — NC 데이터는 CAD 형면으로, 상형 형면 오프셋은 수직 t (법선 오프셋 아님) · 벽이 수직이라 펀치 옆면은 윤곽 그대로, 펀치 R 은 CAD 에서</t>
         </is>
       </c>
     </row>
@@ -1153,11 +1153,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>997 kg × 3,000</t>
+          <t>981 kg × 3,000</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2992145</v>
+        <v>2943030</v>
       </c>
     </row>
     <row r="6">
@@ -1168,11 +1168,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>139 kg × 4,000</t>
+          <t>167 kg × 4,000</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>557888</v>
+        <v>669319</v>
       </c>
     </row>
     <row r="7">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1,137 kg × 600</t>
+          <t>1,148 kg × 600</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>682112</v>
+        <v>689004</v>
       </c>
     </row>
     <row r="8">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1552473</v>
+        <v>1559393</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1707720</v>
+        <v>1715333</v>
       </c>
     </row>
     <row r="15">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>18784919</v>
+        <v>18868660</v>
       </c>
     </row>
   </sheetData>

--- a/unfold/samples/castdie/oil_pan_t1_드로우금형_부품표.xlsx
+++ b/unfold/samples/castdie/oil_pan_t1_드로우금형_부품표.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부품표" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금형비" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="하중-행정" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -639,11 +640,11 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>655.3</v>
+        <v>655.0700000000001</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>형면 = 제품 면 + t 1 오프셋 (수직 오프셋 어림), 다이 R5 화염 경화 · 위 리브</t>
+          <t>형면 = 펀치 형면의 법선 오프셋 t 1 (수직 성분 t·√(1+|∇h|²)), 다이 R5 화염 경화 · 위 리브</t>
         </is>
       </c>
     </row>
@@ -914,12 +915,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>프레스 300톤 (필요 62 tf, 행정 ≥ 278)</t>
+          <t>프레스 300톤 (필요 104 tf, 행정 ≥ 278)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(드로잉 387 + 누르개 83 kN) × 1.3, 깊이 109 위에서</t>
+          <t>모든 깊이에서 (드로잉 + 누르개) × 1.3 ≤ 톤수 곡선 — 꼭대기 401 kN 이 깊이 9 (하사점 위 100)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -931,17 +932,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>쿠션 핀 수</t>
+          <t>드로잉비 β</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4 개</t>
+          <t>1.36 (d 425 ← D₀ 577)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>≥ 83 kN ÷ 40 = 4</t>
+          <t>≤ LDR 2.21 (Whiteley · Hosford, r̄ 1.3)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -953,17 +954,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>가이드 물림 (열림)</t>
+          <t>다이 R</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>61 mm</t>
+          <t>R5 = 5.0 t</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>≥ 30 mm (블랭크 넣을 때도 안내)</t>
+          <t>5 ~ 10 t (4ming) · Oehler 권장 R5.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -975,17 +976,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>누르개 면압</t>
+          <t>쿠션 핀 수</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.5 MPa</t>
+          <t>4 개</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1 ~ 3 MPa (연강)</t>
+          <t>≥ 77 kN ÷ 40 = 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -997,17 +998,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>에어 벤트</t>
+          <t>가이드 물림 (열림)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3 개</t>
+          <t>61 mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>≥ 1 (형면 낮은 곳)</t>
+          <t>≥ 30 mm (블랭크 넣을 때도 안내)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1019,20 +1020,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>누르개 밑 ↔ 베이스 (하사점)</t>
+          <t>누르개 면압</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10 mm</t>
+          <t>Siebel 2.33 MPa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>≥ 10 (밸런스 블록 위)</t>
+          <t>≤ 표 값 2.5 MPa (쿠션 능력 상한)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
+        <is>
+          <t>적합</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>에어 벤트</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3 개</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>≥ 1 (형면 낮은 곳)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>적합</t>
         </is>
@@ -1041,47 +1064,76 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>• OP10 드로잉 (주물 금형): 깊이 109 mm · 바인더 347 × 447 · 다이 R5 · 벽 10°</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>• 드로잉력 F = 펀치 둘레 1,336 × t 1 × UTS 414 × 0.7 = 387 kN, 누르개 힘 = 바인더 0.033 m² × 2.5 MPa = 83 kN → 프레스 62 tf — 프레스 300톤</t>
+          <t>누르개 밑 ↔ 베이스 (하사점)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10 mm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>≥ 10 (밸런스 블록 위)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>적합</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>• 높이: 닫힌 500 · 열린 669 mm · 행정 ≥ 278 (깊이 × 2 + 틈 60)</t>
+          <t>• OP10 드로잉 (주물 금형): 깊이 109 mm · 바인더 347 × 447 · 다이 R5 · 벽 10°</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>• 주물 무게 어림 1,226 kg (리브 · 빈 곳 판 솔리드 × 7.2) — 베이스 326 · 펀치 107 · 누르개 60 · 상형 655</t>
+          <t>• 드로잉력: 같은 둘레 원통 d = 1,336 / π = 425, 블랭크 D₀ = √(4 × 0.261 m² / π) = 577 (β 1.36) — 교재 표 π d t σb n(m) 291 kN / Siebel π d t · 1.1 k_fm ln β / η_F 0.65 + 2 μ F_N 333 kN 중 큰 값 333 kN (UTS 414 · n 0.19)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>• 형면은 격자 9 mm 의 B-스플라인 근사 (다이 R · 벽은 뭉뚱그려짐) — NC 데이터는 CAD 형면으로, 상형 형면 오프셋은 수직 t (법선 오프셋 아님) · 벽이 수직이라 펀치 옆면은 윤곽 그대로, 펀치 R 은 CAD 에서</t>
+          <t>• 누르개 힘 = Siebel 면압 [(β − 1)^k + d / 200 s] Rm / 400 = 2.33 MPa × 고리 0.033 m² = 77 kN (표 값 2.5 MPa 면 83 kN — 쿠션 능력 상한) → 프레스 104 tf — 프레스 300톤, 하중 꼭대기는 깊이 9 mm (하중 - 행정 곡선은 부품표 엑셀)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>• 드로우 비드 · 누르개 면압 · 스프링백 보정은 시타 (트라이아웃) 로 — 비드 자리는 성형 해석 draw-in 이 큰 변</t>
+          <t>• 높이: 닫힌 500 · 열린 669 mm · 행정 ≥ 278 (깊이 × 2 + 틈 60)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
+        <is>
+          <t>• 주물 무게 어림 1,226 kg (리브 · 빈 곳 판 솔리드 × 7.2) — 베이스 326 · 펀치 107 · 누르개 60 · 상형 655</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>• 형면은 격자 9 mm 의 쌍선형 면 근사 (다이 R · 벽은 뭉뚱그려짐) — NC 데이터는 CAD 형면으로, 상형 형면 = 펀치 형면의 법선 오프셋 t (수직 성분 t·√(1+|∇h|²), 경사 70° 넘는 벽은 × 3 상한) · 벽이 수직이라 펀치 옆면은 윤곽 그대로, 펀치 R 은 CAD 에서</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>• 드로우 비드 · 누르개 면압 · 스프링백 보정은 시타 (트라이아웃) 로 — 비드 자리는 성형 해석 draw-in 이 큰 변</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>• 표준품 (가이드 · 쿠션 핀 · 마모판) 치수는 일반값 — MISUMI · 후타바 대형 금형 표로 확인</t>
         </is>
@@ -1157,7 +1209,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2943030</v>
+        <v>2942356</v>
       </c>
     </row>
     <row r="6">
@@ -1187,7 +1239,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>689004</v>
+        <v>688869</v>
       </c>
     </row>
     <row r="8">
@@ -1277,7 +1329,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1559393</v>
+        <v>1559312</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1344,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1715333</v>
+        <v>1715244</v>
       </c>
     </row>
     <row r="15">
@@ -1302,7 +1354,1268 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>18868660</v>
+        <v>18867680</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>드로잉 하중 - 행정 곡선 (같은 둘레 원통 Siebel) — d 425 · D₀ 577 · β 1.36 · 면압 2.33 MPa · 프레스 프레스 300톤</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>펀치 깊이 mm</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>드로잉력 kN</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>누르개 kN</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>합 kN</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>× 안전율 kN</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>프레스 능력 kN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1483.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B5" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>205</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1486.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="B6" t="n">
+        <v>161.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>235.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1489.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>238.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>310.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>404</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1493.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>498.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1497.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="B9" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>401.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>521.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1501.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>67</v>
+      </c>
+      <c r="D10" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>511.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1506.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>320.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>501.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1512.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="B12" t="n">
+        <v>314.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>378.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>491.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1517.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="B13" t="n">
+        <v>308.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>481.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1523.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>302</v>
+      </c>
+      <c r="C14" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>470.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1530.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="B15" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>460.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1537.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="B16" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>450.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1544.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B17" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>439.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1552.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="B18" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1561.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="B19" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1570.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="B20" t="n">
+        <v>263.2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>407.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1579.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="B21" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1589.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="B22" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1600.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>45</v>
+      </c>
+      <c r="D23" t="n">
+        <v>287.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1611.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="B24" t="n">
+        <v>236</v>
+      </c>
+      <c r="C24" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1623.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="B25" t="n">
+        <v>229</v>
+      </c>
+      <c r="C25" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>351.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1636.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="B26" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>261.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1650.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B27" t="n">
+        <v>214.7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>253</v>
+      </c>
+      <c r="E27" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1664.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="B28" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>317.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1679.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="B29" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>235</v>
+      </c>
+      <c r="E29" t="n">
+        <v>305.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1695.7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>48</v>
+      </c>
+      <c r="B30" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>293.7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1712.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="B31" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>216.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>281.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1730.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="B32" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1750.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="B33" t="n">
+        <v>170</v>
+      </c>
+      <c r="C33" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1770.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="B34" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>245.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1792.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="B35" t="n">
+        <v>154.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>179</v>
+      </c>
+      <c r="E35" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1815.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>23</v>
+      </c>
+      <c r="D36" t="n">
+        <v>169.4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1840.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>61</v>
+      </c>
+      <c r="B37" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="E37" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1866.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="B38" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D38" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1895.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="B39" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1925.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B40" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1958.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="B41" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="C41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1993.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2031.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2072.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="C44" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>88</v>
+      </c>
+      <c r="E44" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2117.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="B45" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="C45" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2165.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="B46" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E46" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2219.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="B47" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2277.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="B48" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D48" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2342.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="B49" t="n">
+        <v>32</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>33</v>
+      </c>
+      <c r="E49" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>85</v>
+      </c>
+      <c r="B50" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2495.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="B51" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2587.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2691.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2811.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>109</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2942</v>
       </c>
     </row>
   </sheetData>
